--- a/MainTop/17.09.2026 бирки г10/x10_print_sorted.xlsx
+++ b/MainTop/17.09.2026 бирки г10/x10_print_sorted.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\17.09.2026 бирки г10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98010C7-FE99-4575-80C8-401A7DA505E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BB06CF-1EE7-4598-AFEB-789C3D2EC497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -423,13 +423,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,7 +443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -456,69 +456,89 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <f>B2*8</f>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F14" si="0">B3*8</f>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B5" s="1">
         <v>8</v>
       </c>
-      <c r="B4" s="1">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1">
-        <v>16</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B7" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -526,13 +546,17 @@
       <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -540,8 +564,12 @@
       <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -554,13 +582,17 @@
       <c r="D9" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -568,13 +600,17 @@
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -582,13 +618,17 @@
       <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -596,13 +636,17 @@
       <c r="D12" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -610,8 +654,12 @@
       <c r="D13" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -623,6 +671,10 @@
       </c>
       <c r="D14" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
